--- a/artfynd/A 27059-2021 artfynd.xlsx
+++ b/artfynd/A 27059-2021 artfynd.xlsx
@@ -15436,7 +15436,7 @@
         <v>0</v>
       </c>
       <c r="AE133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG133" t="b">
         <v>0</v>
@@ -15887,7 +15887,7 @@
         <v>0</v>
       </c>
       <c r="AE137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
@@ -16008,7 +16008,7 @@
         <v>0</v>
       </c>
       <c r="AE138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
